--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111931635</v>
+        <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>93189</v>
+        <v>91542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,40 +1595,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>3286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Strömsbergs bruk/spökskogen, Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642301</v>
+        <v>642117</v>
       </c>
       <c r="R10" t="n">
-        <v>6698305</v>
+        <v>6698299</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,12 +1653,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,16 +1681,6 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1694,13 +1695,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111931635</t>
+          <t>https://artportalen.se/Sighting/136755007</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128344358</v>
+        <v>111931635</v>
       </c>
       <c r="B11" t="n">
         <v>93189</v>
@@ -1728,27 +1729,23 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bauerskogen, Upl</t>
+          <t>Strömsbergs bruk/spökskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642101</v>
+        <v>642301</v>
       </c>
       <c r="R11" t="n">
-        <v>6698271</v>
+        <v>6698305</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,12 +1769,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,6 +1787,16 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1804,16 +1811,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344358</t>
+          <t>https://artportalen.se/Sighting/111931635</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111979876</v>
+        <v>128344358</v>
       </c>
       <c r="B12" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,26 +1828,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1848,17 +1855,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Strömsbergs bruk , Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>642175</v>
+        <v>642101</v>
       </c>
       <c r="R12" t="n">
-        <v>6698320</v>
+        <v>6698271</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,22 +1889,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,16 +1921,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111979876</t>
+          <t>https://artportalen.se/Sighting/128344358</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111980195</v>
+        <v>111979876</v>
       </c>
       <c r="B13" t="n">
-        <v>93215</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,35 +1938,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tierp, Upl</t>
+          <t>Strömsbergs bruk , Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>642103</v>
+        <v>642175</v>
       </c>
       <c r="R13" t="n">
-        <v>6698251</v>
+        <v>6698320</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,7 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,6 +2023,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2037,13 +2041,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111980195</t>
+          <t>https://artportalen.se/Sighting/111979876</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128344230</v>
+        <v>111980195</v>
       </c>
       <c r="B14" t="n">
         <v>93215</v>
@@ -2071,27 +2075,21 @@
           <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bauerskogen, Upl</t>
+          <t>Tierp, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>642117</v>
+        <v>642103</v>
       </c>
       <c r="R14" t="n">
-        <v>6698299</v>
+        <v>6698251</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,12 +2113,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,7 +2137,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2147,59 +2154,61 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344230</t>
+          <t>https://artportalen.se/Sighting/111980195</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112030310</v>
+        <v>128344230</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>93215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strömsbergs bruk/spökskogen, Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>642301</v>
+        <v>642117</v>
       </c>
       <c r="R15" t="n">
-        <v>6698305</v>
+        <v>6698299</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2223,22 +2232,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,6 +2246,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2263,6 +2263,123 @@
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344230</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112030310</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Strömsbergs bruk/spökskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>642301</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6698305</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112030310</t>
         </is>
@@ -2284,6 +2401,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91542</v>
+        <v>91544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91544</v>
+        <v>91546</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91546</v>
+        <v>91548</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91548</v>
+        <v>91550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91550</v>
+        <v>91551</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91551</v>
+        <v>91557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91563</v>
+        <v>91576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91576</v>
+        <v>91578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91581</v>
+        <v>91591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1587,7 +1587,7 @@
         <v>136755007</v>
       </c>
       <c r="B10" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
